--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464334</v>
+        <v>124464176</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878794</v>
+        <v>878858</v>
       </c>
       <c r="R2" t="n">
-        <v>7378006</v>
+        <v>7377931</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464339</v>
+        <v>124464172</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878916</v>
+        <v>879038</v>
       </c>
       <c r="R3" t="n">
-        <v>7377843</v>
+        <v>7377791</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464332</v>
+        <v>124464166</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878883</v>
+        <v>878884</v>
       </c>
       <c r="R5" t="n">
-        <v>7377894</v>
+        <v>7377762</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1059,11 +1059,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1076,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464176</v>
+        <v>124464335</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878858</v>
+        <v>879043</v>
       </c>
       <c r="R6" t="n">
-        <v>7377931</v>
+        <v>7377785</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1166,6 +1161,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464171</v>
+        <v>124464336</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878938</v>
+        <v>878805</v>
       </c>
       <c r="R7" t="n">
-        <v>7377766</v>
+        <v>7377987</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1268,6 +1268,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464335</v>
+        <v>124464339</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879043</v>
+        <v>878916</v>
       </c>
       <c r="R8" t="n">
-        <v>7377785</v>
+        <v>7377843</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464165</v>
+        <v>124464338</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878976</v>
+        <v>878878</v>
       </c>
       <c r="R9" t="n">
-        <v>7377902</v>
+        <v>7378047</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1477,11 +1477,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1494,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464168</v>
+        <v>124464333</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878777</v>
+        <v>879031</v>
       </c>
       <c r="R10" t="n">
-        <v>7377974</v>
+        <v>7377846</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1596,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464174</v>
+        <v>124464331</v>
       </c>
       <c r="B11" t="n">
-        <v>92490</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878886</v>
+        <v>878850</v>
       </c>
       <c r="R11" t="n">
-        <v>7377893</v>
+        <v>7378069</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1686,6 +1681,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464172</v>
+        <v>124464174</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>92490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879038</v>
+        <v>878886</v>
       </c>
       <c r="R12" t="n">
-        <v>7377791</v>
+        <v>7377893</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464336</v>
+        <v>124464180</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878805</v>
+        <v>878981</v>
       </c>
       <c r="R13" t="n">
-        <v>7377987</v>
+        <v>7377864</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1890,11 +1890,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1907,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464180</v>
+        <v>124464171</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878981</v>
+        <v>878938</v>
       </c>
       <c r="R14" t="n">
-        <v>7377864</v>
+        <v>7377766</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2021,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464338</v>
+        <v>124464340</v>
       </c>
       <c r="B15" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878878</v>
+        <v>878814</v>
       </c>
       <c r="R15" t="n">
-        <v>7378047</v>
+        <v>7378040</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2332,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464333</v>
+        <v>124464168</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>79920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879031</v>
+        <v>878777</v>
       </c>
       <c r="R18" t="n">
-        <v>7377846</v>
+        <v>7377974</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2422,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464331</v>
+        <v>124464332</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878850</v>
+        <v>878883</v>
       </c>
       <c r="R19" t="n">
-        <v>7378069</v>
+        <v>7377894</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2514,7 +2509,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2541,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464166</v>
+        <v>124464334</v>
       </c>
       <c r="B20" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878884</v>
+        <v>878794</v>
       </c>
       <c r="R20" t="n">
-        <v>7377762</v>
+        <v>7378006</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2631,22 +2626,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464340</v>
+        <v>124464165</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878814</v>
+        <v>878976</v>
       </c>
       <c r="R21" t="n">
-        <v>7378040</v>
+        <v>7377902</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2721,6 +2716,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464176</v>
+        <v>124464333</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878858</v>
+        <v>879031</v>
       </c>
       <c r="R2" t="n">
-        <v>7377931</v>
+        <v>7377846</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464172</v>
+        <v>124464177</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879038</v>
+        <v>879054</v>
       </c>
       <c r="R3" t="n">
-        <v>7377791</v>
+        <v>7377801</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464170</v>
+        <v>124464332</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878795</v>
+        <v>878883</v>
       </c>
       <c r="R4" t="n">
-        <v>7377998</v>
+        <v>7377894</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -957,6 +962,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -969,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464166</v>
+        <v>124464178</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878884</v>
+        <v>878957</v>
       </c>
       <c r="R5" t="n">
-        <v>7377762</v>
+        <v>7377759</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464335</v>
+        <v>124464180</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879043</v>
+        <v>878981</v>
       </c>
       <c r="R6" t="n">
-        <v>7377785</v>
+        <v>7377864</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1161,11 +1171,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464336</v>
+        <v>124464171</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878805</v>
+        <v>878938</v>
       </c>
       <c r="R7" t="n">
-        <v>7377987</v>
+        <v>7377766</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1268,11 +1273,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1285,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464339</v>
+        <v>124464168</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878916</v>
+        <v>878777</v>
       </c>
       <c r="R8" t="n">
-        <v>7377843</v>
+        <v>7377974</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464338</v>
+        <v>124464176</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878878</v>
+        <v>878858</v>
       </c>
       <c r="R9" t="n">
-        <v>7378047</v>
+        <v>7377931</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1489,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464333</v>
+        <v>124464339</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>879031</v>
+        <v>878916</v>
       </c>
       <c r="R10" t="n">
-        <v>7377846</v>
+        <v>7377843</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464331</v>
+        <v>124464166</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878850</v>
+        <v>878884</v>
       </c>
       <c r="R11" t="n">
-        <v>7378069</v>
+        <v>7377762</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1681,11 +1681,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464174</v>
+        <v>124464336</v>
       </c>
       <c r="B12" t="n">
-        <v>92490</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878886</v>
+        <v>878805</v>
       </c>
       <c r="R12" t="n">
-        <v>7377893</v>
+        <v>7377987</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1788,6 +1783,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1800,22 +1800,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464180</v>
+        <v>124464172</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878981</v>
+        <v>879038</v>
       </c>
       <c r="R13" t="n">
-        <v>7377864</v>
+        <v>7377791</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464171</v>
+        <v>124464331</v>
       </c>
       <c r="B14" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878938</v>
+        <v>878850</v>
       </c>
       <c r="R14" t="n">
-        <v>7377766</v>
+        <v>7378069</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1992,6 +1992,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2004,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464340</v>
+        <v>124464334</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2033,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878814</v>
+        <v>878794</v>
       </c>
       <c r="R15" t="n">
-        <v>7378040</v>
+        <v>7378006</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464177</v>
+        <v>124464340</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2135,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879054</v>
+        <v>878814</v>
       </c>
       <c r="R16" t="n">
-        <v>7377801</v>
+        <v>7378040</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2196,11 +2201,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2213,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464178</v>
+        <v>124464338</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878957</v>
+        <v>878878</v>
       </c>
       <c r="R17" t="n">
-        <v>7377759</v>
+        <v>7378047</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,22 +2315,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464168</v>
+        <v>124464165</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878777</v>
+        <v>878976</v>
       </c>
       <c r="R18" t="n">
-        <v>7377974</v>
+        <v>7377902</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2403,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464332</v>
+        <v>124464335</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878883</v>
+        <v>879043</v>
       </c>
       <c r="R19" t="n">
-        <v>7377894</v>
+        <v>7377785</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2509,7 +2514,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464334</v>
+        <v>124464174</v>
       </c>
       <c r="B20" t="n">
-        <v>91023</v>
+        <v>92490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1205</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878794</v>
+        <v>878886</v>
       </c>
       <c r="R20" t="n">
-        <v>7378006</v>
+        <v>7377893</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2626,22 +2631,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464165</v>
+        <v>124464170</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878976</v>
+        <v>878795</v>
       </c>
       <c r="R21" t="n">
-        <v>7377902</v>
+        <v>7377998</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2714,11 +2719,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464333</v>
+        <v>124464180</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879031</v>
+        <v>878981</v>
       </c>
       <c r="R2" t="n">
-        <v>7377846</v>
+        <v>7377864</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464177</v>
+        <v>124464165</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879054</v>
+        <v>878976</v>
       </c>
       <c r="R3" t="n">
-        <v>7377801</v>
+        <v>7377902</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464332</v>
+        <v>124464331</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878883</v>
+        <v>878850</v>
       </c>
       <c r="R4" t="n">
-        <v>7377894</v>
+        <v>7378069</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464178</v>
+        <v>124464170</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878957</v>
+        <v>878795</v>
       </c>
       <c r="R5" t="n">
-        <v>7377759</v>
+        <v>7377998</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464180</v>
+        <v>124464338</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878981</v>
+        <v>878878</v>
       </c>
       <c r="R6" t="n">
-        <v>7377864</v>
+        <v>7378047</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1183,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464171</v>
+        <v>124464176</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878938</v>
+        <v>878858</v>
       </c>
       <c r="R7" t="n">
-        <v>7377766</v>
+        <v>7377931</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464168</v>
+        <v>124464340</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878777</v>
+        <v>878814</v>
       </c>
       <c r="R8" t="n">
-        <v>7377974</v>
+        <v>7378040</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464176</v>
+        <v>124464166</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>79920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878858</v>
+        <v>878884</v>
       </c>
       <c r="R9" t="n">
-        <v>7377931</v>
+        <v>7377762</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464339</v>
+        <v>124464171</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878916</v>
+        <v>878938</v>
       </c>
       <c r="R10" t="n">
-        <v>7377843</v>
+        <v>7377766</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1591,22 +1591,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464166</v>
+        <v>124464332</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878884</v>
+        <v>878883</v>
       </c>
       <c r="R11" t="n">
-        <v>7377762</v>
+        <v>7377894</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1681,6 +1681,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1693,12 +1698,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464172</v>
+        <v>124464177</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879038</v>
+        <v>879054</v>
       </c>
       <c r="R13" t="n">
-        <v>7377791</v>
+        <v>7377801</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1888,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464331</v>
+        <v>124464168</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878850</v>
+        <v>878777</v>
       </c>
       <c r="R14" t="n">
-        <v>7378069</v>
+        <v>7377974</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1992,11 +2002,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2009,12 +2014,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2123,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464340</v>
+        <v>124464339</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878814</v>
+        <v>878916</v>
       </c>
       <c r="R16" t="n">
-        <v>7378040</v>
+        <v>7377843</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464338</v>
+        <v>124464174</v>
       </c>
       <c r="B17" t="n">
-        <v>56714</v>
+        <v>92490</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878878</v>
+        <v>878886</v>
       </c>
       <c r="R17" t="n">
-        <v>7378047</v>
+        <v>7377893</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2315,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464165</v>
+        <v>124464178</v>
       </c>
       <c r="B18" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878976</v>
+        <v>878957</v>
       </c>
       <c r="R18" t="n">
-        <v>7377902</v>
+        <v>7377759</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2403,11 +2408,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,7 +2434,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464335</v>
+        <v>124464172</v>
       </c>
       <c r="B19" t="n">
         <v>57529</v>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879043</v>
+        <v>879038</v>
       </c>
       <c r="R19" t="n">
-        <v>7377785</v>
+        <v>7377791</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2512,11 +2512,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2529,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464174</v>
+        <v>124464335</v>
       </c>
       <c r="B20" t="n">
-        <v>92490</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878886</v>
+        <v>879043</v>
       </c>
       <c r="R20" t="n">
-        <v>7377893</v>
+        <v>7377785</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2619,6 +2614,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2631,22 +2631,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464170</v>
+        <v>124464333</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878795</v>
+        <v>879031</v>
       </c>
       <c r="R21" t="n">
-        <v>7377998</v>
+        <v>7377846</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464180</v>
+        <v>124464333</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878981</v>
+        <v>879031</v>
       </c>
       <c r="R2" t="n">
-        <v>7377864</v>
+        <v>7377846</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464165</v>
+        <v>124464168</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878976</v>
+        <v>878777</v>
       </c>
       <c r="R3" t="n">
-        <v>7377902</v>
+        <v>7377974</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464331</v>
+        <v>124464340</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878850</v>
+        <v>878814</v>
       </c>
       <c r="R4" t="n">
-        <v>7378069</v>
+        <v>7378040</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464170</v>
+        <v>124464174</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>92490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878795</v>
+        <v>878886</v>
       </c>
       <c r="R5" t="n">
-        <v>7377998</v>
+        <v>7377893</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464338</v>
+        <v>124464334</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878878</v>
+        <v>878794</v>
       </c>
       <c r="R6" t="n">
-        <v>7378047</v>
+        <v>7378006</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1195,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464176</v>
+        <v>124464332</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878858</v>
+        <v>878883</v>
       </c>
       <c r="R7" t="n">
-        <v>7377931</v>
+        <v>7377894</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1273,6 +1263,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1285,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464340</v>
+        <v>124464172</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878814</v>
+        <v>879038</v>
       </c>
       <c r="R8" t="n">
-        <v>7378040</v>
+        <v>7377791</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1387,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464166</v>
+        <v>124464331</v>
       </c>
       <c r="B9" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878884</v>
+        <v>878850</v>
       </c>
       <c r="R9" t="n">
-        <v>7377762</v>
+        <v>7378069</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1477,6 +1472,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1489,12 +1489,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464332</v>
+        <v>124464176</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878883</v>
+        <v>878858</v>
       </c>
       <c r="R11" t="n">
-        <v>7377894</v>
+        <v>7377931</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1681,11 +1681,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1698,22 +1693,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464336</v>
+        <v>124464170</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878805</v>
+        <v>878795</v>
       </c>
       <c r="R12" t="n">
-        <v>7377987</v>
+        <v>7377998</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1788,11 +1783,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1805,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464177</v>
+        <v>124464166</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879054</v>
+        <v>878884</v>
       </c>
       <c r="R13" t="n">
-        <v>7377801</v>
+        <v>7377762</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1893,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464168</v>
+        <v>124464336</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878777</v>
+        <v>878805</v>
       </c>
       <c r="R14" t="n">
-        <v>7377974</v>
+        <v>7377987</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2002,6 +1987,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2014,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464334</v>
+        <v>124464177</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878794</v>
+        <v>879054</v>
       </c>
       <c r="R15" t="n">
-        <v>7378006</v>
+        <v>7377801</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2104,6 +2094,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2116,19 +2111,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464339</v>
+        <v>124464180</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878916</v>
+        <v>878981</v>
       </c>
       <c r="R16" t="n">
-        <v>7377843</v>
+        <v>7377864</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2218,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464174</v>
+        <v>124464165</v>
       </c>
       <c r="B17" t="n">
-        <v>92490</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878886</v>
+        <v>878976</v>
       </c>
       <c r="R17" t="n">
-        <v>7377893</v>
+        <v>7377902</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2306,6 +2301,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2434,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464172</v>
+        <v>124464339</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879038</v>
+        <v>878916</v>
       </c>
       <c r="R19" t="n">
-        <v>7377791</v>
+        <v>7377843</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2524,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464335</v>
+        <v>124464338</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,16 +2552,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>879043</v>
+        <v>878878</v>
       </c>
       <c r="R20" t="n">
-        <v>7377785</v>
+        <v>7378047</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2612,11 +2612,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464333</v>
+        <v>124464335</v>
       </c>
       <c r="B21" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879031</v>
+        <v>879043</v>
       </c>
       <c r="R21" t="n">
-        <v>7377846</v>
+        <v>7377785</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2719,6 +2714,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -2016,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464177</v>
+        <v>124464180</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879054</v>
+        <v>878981</v>
       </c>
       <c r="R15" t="n">
-        <v>7377801</v>
+        <v>7377864</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2092,11 +2092,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464180</v>
+        <v>124464177</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2135,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878981</v>
+        <v>879054</v>
       </c>
       <c r="R16" t="n">
-        <v>7377864</v>
+        <v>7377801</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2199,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464338</v>
+        <v>124464335</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,16 +2552,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878878</v>
+        <v>879043</v>
       </c>
       <c r="R20" t="n">
-        <v>7378047</v>
+        <v>7377785</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2612,6 +2612,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464335</v>
+        <v>124464338</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,16 +2659,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2678,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879043</v>
+        <v>878878</v>
       </c>
       <c r="R21" t="n">
-        <v>7377785</v>
+        <v>7378047</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2714,11 +2719,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464333</v>
+        <v>124464166</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879031</v>
+        <v>878884</v>
       </c>
       <c r="R2" t="n">
-        <v>7377846</v>
+        <v>7377762</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464168</v>
+        <v>124464333</v>
       </c>
       <c r="B3" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878777</v>
+        <v>879031</v>
       </c>
       <c r="R3" t="n">
-        <v>7377974</v>
+        <v>7377846</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464174</v>
+        <v>124464178</v>
       </c>
       <c r="B5" t="n">
-        <v>92490</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878886</v>
+        <v>878957</v>
       </c>
       <c r="R5" t="n">
-        <v>7377893</v>
+        <v>7377759</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464334</v>
+        <v>124464332</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878794</v>
+        <v>878883</v>
       </c>
       <c r="R6" t="n">
-        <v>7378006</v>
+        <v>7377894</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464332</v>
+        <v>124464176</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878883</v>
+        <v>878858</v>
       </c>
       <c r="R7" t="n">
-        <v>7377894</v>
+        <v>7377931</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1263,11 +1268,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464172</v>
+        <v>124464171</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879038</v>
+        <v>878938</v>
       </c>
       <c r="R8" t="n">
-        <v>7377791</v>
+        <v>7377766</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464331</v>
+        <v>124464339</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878850</v>
+        <v>878916</v>
       </c>
       <c r="R9" t="n">
-        <v>7378069</v>
+        <v>7377843</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1470,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464171</v>
+        <v>124464165</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878938</v>
+        <v>878976</v>
       </c>
       <c r="R10" t="n">
-        <v>7377766</v>
+        <v>7377902</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1577,6 +1572,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464176</v>
+        <v>124464338</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878858</v>
+        <v>878878</v>
       </c>
       <c r="R11" t="n">
-        <v>7377931</v>
+        <v>7378047</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1693,12 +1693,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464166</v>
+        <v>124464335</v>
       </c>
       <c r="B13" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878884</v>
+        <v>879043</v>
       </c>
       <c r="R13" t="n">
-        <v>7377762</v>
+        <v>7377785</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1885,6 +1885,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1897,19 +1902,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464336</v>
+        <v>124464177</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878805</v>
+        <v>879054</v>
       </c>
       <c r="R14" t="n">
-        <v>7377987</v>
+        <v>7377801</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1989,7 +1994,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.5 m2</t>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464180</v>
+        <v>124464331</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878981</v>
+        <v>878850</v>
       </c>
       <c r="R15" t="n">
-        <v>7377864</v>
+        <v>7378069</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2094,6 +2099,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2106,22 +2116,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464177</v>
+        <v>124464180</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2140,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879054</v>
+        <v>878981</v>
       </c>
       <c r="R16" t="n">
-        <v>7377801</v>
+        <v>7377864</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2194,11 +2204,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464165</v>
+        <v>124464336</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878976</v>
+        <v>878805</v>
       </c>
       <c r="R17" t="n">
-        <v>7377902</v>
+        <v>7377987</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2305,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>0.5 m2</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464178</v>
+        <v>124464172</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2349,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878957</v>
+        <v>879038</v>
       </c>
       <c r="R18" t="n">
-        <v>7377759</v>
+        <v>7377791</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2434,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464339</v>
+        <v>124464334</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2451,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878916</v>
+        <v>878794</v>
       </c>
       <c r="R19" t="n">
-        <v>7377843</v>
+        <v>7378006</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2536,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464335</v>
+        <v>124464174</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>92490</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>879043</v>
+        <v>878886</v>
       </c>
       <c r="R20" t="n">
-        <v>7377785</v>
+        <v>7377893</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2614,11 +2619,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2631,22 +2631,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464338</v>
+        <v>124464168</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878878</v>
+        <v>878777</v>
       </c>
       <c r="R21" t="n">
-        <v>7378047</v>
+        <v>7377974</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464333</v>
+        <v>124464340</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879031</v>
+        <v>878814</v>
       </c>
       <c r="R3" t="n">
-        <v>7377846</v>
+        <v>7378040</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464340</v>
+        <v>124464333</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878814</v>
+        <v>879031</v>
       </c>
       <c r="R4" t="n">
-        <v>7378040</v>
+        <v>7377846</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464166</v>
+        <v>124464334</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878884</v>
+        <v>878794</v>
       </c>
       <c r="R2" t="n">
-        <v>7377762</v>
+        <v>7378006</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464340</v>
+        <v>124464333</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878814</v>
+        <v>879031</v>
       </c>
       <c r="R3" t="n">
-        <v>7378040</v>
+        <v>7377846</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464333</v>
+        <v>124464339</v>
       </c>
       <c r="B4" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879031</v>
+        <v>878916</v>
       </c>
       <c r="R4" t="n">
-        <v>7377846</v>
+        <v>7377843</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464178</v>
+        <v>124464336</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878957</v>
+        <v>878805</v>
       </c>
       <c r="R5" t="n">
-        <v>7377759</v>
+        <v>7377987</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1059,6 +1059,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1071,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464332</v>
+        <v>124464178</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878883</v>
+        <v>878957</v>
       </c>
       <c r="R6" t="n">
-        <v>7377894</v>
+        <v>7377759</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1161,11 +1166,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464176</v>
+        <v>124464335</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878858</v>
+        <v>879043</v>
       </c>
       <c r="R7" t="n">
-        <v>7377931</v>
+        <v>7377785</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1268,6 +1268,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464171</v>
+        <v>124464172</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878938</v>
+        <v>879038</v>
       </c>
       <c r="R8" t="n">
-        <v>7377766</v>
+        <v>7377791</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464339</v>
+        <v>124464177</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878916</v>
+        <v>879054</v>
       </c>
       <c r="R9" t="n">
-        <v>7377843</v>
+        <v>7377801</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,6 +1477,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1484,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464165</v>
+        <v>124464331</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878976</v>
+        <v>878850</v>
       </c>
       <c r="R10" t="n">
-        <v>7377902</v>
+        <v>7378069</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1576,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464338</v>
+        <v>124464176</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878878</v>
+        <v>878858</v>
       </c>
       <c r="R11" t="n">
-        <v>7378047</v>
+        <v>7377931</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1693,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464170</v>
+        <v>124464332</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878795</v>
+        <v>878883</v>
       </c>
       <c r="R12" t="n">
-        <v>7377998</v>
+        <v>7377894</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1783,6 +1793,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1795,22 +1810,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464335</v>
+        <v>124464165</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879043</v>
+        <v>878976</v>
       </c>
       <c r="R13" t="n">
-        <v>7377785</v>
+        <v>7377902</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1887,7 +1902,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,22 +1917,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464177</v>
+        <v>124464168</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1941,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879054</v>
+        <v>878777</v>
       </c>
       <c r="R14" t="n">
-        <v>7377801</v>
+        <v>7377974</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1990,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464331</v>
+        <v>124464338</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,16 +2047,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2061,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878850</v>
+        <v>878878</v>
       </c>
       <c r="R15" t="n">
-        <v>7378069</v>
+        <v>7378047</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2097,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464336</v>
+        <v>124464171</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>91023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2247,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878805</v>
+        <v>878938</v>
       </c>
       <c r="R17" t="n">
-        <v>7377987</v>
+        <v>7377766</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2308,11 +2313,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2325,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464172</v>
+        <v>124464340</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879038</v>
+        <v>878814</v>
       </c>
       <c r="R18" t="n">
-        <v>7377791</v>
+        <v>7378040</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,22 +2427,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464334</v>
+        <v>124464170</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878794</v>
+        <v>878795</v>
       </c>
       <c r="R19" t="n">
-        <v>7378006</v>
+        <v>7377998</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2529,22 +2529,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464174</v>
+        <v>124464166</v>
       </c>
       <c r="B20" t="n">
-        <v>92490</v>
+        <v>79920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878886</v>
+        <v>878884</v>
       </c>
       <c r="R20" t="n">
-        <v>7377893</v>
+        <v>7377762</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464168</v>
+        <v>124464174</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>92490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878777</v>
+        <v>878886</v>
       </c>
       <c r="R21" t="n">
-        <v>7377974</v>
+        <v>7377893</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464334</v>
+        <v>124464178</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878794</v>
+        <v>878957</v>
       </c>
       <c r="R2" t="n">
-        <v>7378006</v>
+        <v>7377759</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464333</v>
+        <v>124464171</v>
       </c>
       <c r="B3" t="n">
         <v>91023</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879031</v>
+        <v>878938</v>
       </c>
       <c r="R3" t="n">
-        <v>7377846</v>
+        <v>7377766</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464339</v>
+        <v>124464176</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878916</v>
+        <v>878858</v>
       </c>
       <c r="R4" t="n">
-        <v>7377843</v>
+        <v>7377931</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464336</v>
+        <v>124464180</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878805</v>
+        <v>878981</v>
       </c>
       <c r="R5" t="n">
-        <v>7377987</v>
+        <v>7377864</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1059,11 +1059,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1076,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464178</v>
+        <v>124464177</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878957</v>
+        <v>879054</v>
       </c>
       <c r="R6" t="n">
-        <v>7377759</v>
+        <v>7377801</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1164,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464335</v>
+        <v>124464338</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,16 +1206,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879043</v>
+        <v>878878</v>
       </c>
       <c r="R7" t="n">
-        <v>7377785</v>
+        <v>7378047</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464172</v>
+        <v>124464335</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879038</v>
+        <v>879043</v>
       </c>
       <c r="R8" t="n">
-        <v>7377791</v>
+        <v>7377785</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1375,6 +1370,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1387,19 +1387,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464177</v>
+        <v>124464336</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879054</v>
+        <v>878805</v>
       </c>
       <c r="R9" t="n">
-        <v>7377801</v>
+        <v>7377987</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2 kvm</t>
+          <t>0.5 m2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1494,22 +1494,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464331</v>
+        <v>124464174</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>92490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878850</v>
+        <v>878886</v>
       </c>
       <c r="R10" t="n">
-        <v>7378069</v>
+        <v>7377893</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1584,11 +1584,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1601,22 +1596,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464176</v>
+        <v>124464339</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878858</v>
+        <v>878916</v>
       </c>
       <c r="R11" t="n">
-        <v>7377931</v>
+        <v>7377843</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1703,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464332</v>
+        <v>124464334</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878883</v>
+        <v>878794</v>
       </c>
       <c r="R12" t="n">
-        <v>7377894</v>
+        <v>7378006</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1791,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464165</v>
+        <v>124464168</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878976</v>
+        <v>878777</v>
       </c>
       <c r="R13" t="n">
-        <v>7377902</v>
+        <v>7377974</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1898,11 +1888,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464168</v>
+        <v>124464333</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878777</v>
+        <v>879031</v>
       </c>
       <c r="R14" t="n">
-        <v>7377974</v>
+        <v>7377846</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2019,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464338</v>
+        <v>124464172</v>
       </c>
       <c r="B15" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,16 +2032,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2071,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878878</v>
+        <v>879038</v>
       </c>
       <c r="R15" t="n">
-        <v>7378047</v>
+        <v>7377791</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2121,22 +2106,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464180</v>
+        <v>124464170</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878981</v>
+        <v>878795</v>
       </c>
       <c r="R16" t="n">
-        <v>7377864</v>
+        <v>7377998</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2235,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464171</v>
+        <v>124464340</v>
       </c>
       <c r="B17" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878938</v>
+        <v>878814</v>
       </c>
       <c r="R17" t="n">
-        <v>7377766</v>
+        <v>7378040</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2325,22 +2310,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464340</v>
+        <v>124464331</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878814</v>
+        <v>878850</v>
       </c>
       <c r="R18" t="n">
-        <v>7378040</v>
+        <v>7378069</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2413,6 +2398,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2429,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464170</v>
+        <v>124464166</v>
       </c>
       <c r="B19" t="n">
         <v>79920</v>
@@ -2479,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878795</v>
+        <v>878884</v>
       </c>
       <c r="R19" t="n">
-        <v>7377998</v>
+        <v>7377762</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2541,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464166</v>
+        <v>124464165</v>
       </c>
       <c r="B20" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878884</v>
+        <v>878976</v>
       </c>
       <c r="R20" t="n">
-        <v>7377762</v>
+        <v>7377902</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2617,6 +2607,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464174</v>
+        <v>124464332</v>
       </c>
       <c r="B21" t="n">
-        <v>92490</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2650,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878886</v>
+        <v>878883</v>
       </c>
       <c r="R21" t="n">
-        <v>7377893</v>
+        <v>7377894</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2721,6 +2716,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464178</v>
+        <v>124464333</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878957</v>
+        <v>879031</v>
       </c>
       <c r="R2" t="n">
-        <v>7377759</v>
+        <v>7377846</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464171</v>
+        <v>124464332</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878938</v>
+        <v>878883</v>
       </c>
       <c r="R3" t="n">
-        <v>7377766</v>
+        <v>7377894</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,6 +855,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464176</v>
+        <v>124464336</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878858</v>
+        <v>878805</v>
       </c>
       <c r="R4" t="n">
-        <v>7377931</v>
+        <v>7377987</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -957,6 +962,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -969,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464180</v>
+        <v>124464176</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878981</v>
+        <v>878858</v>
       </c>
       <c r="R5" t="n">
-        <v>7377864</v>
+        <v>7377931</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1190,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464338</v>
+        <v>124464340</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878878</v>
+        <v>878814</v>
       </c>
       <c r="R7" t="n">
-        <v>7378047</v>
+        <v>7378040</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1399,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464336</v>
+        <v>124464180</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878805</v>
+        <v>878981</v>
       </c>
       <c r="R9" t="n">
-        <v>7377987</v>
+        <v>7377864</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1477,11 +1487,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1494,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464174</v>
+        <v>124464334</v>
       </c>
       <c r="B10" t="n">
-        <v>92490</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878886</v>
+        <v>878794</v>
       </c>
       <c r="R10" t="n">
-        <v>7377893</v>
+        <v>7378006</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1596,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464339</v>
+        <v>124464166</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878916</v>
+        <v>878884</v>
       </c>
       <c r="R11" t="n">
-        <v>7377843</v>
+        <v>7377762</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1698,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464334</v>
+        <v>124464168</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878794</v>
+        <v>878777</v>
       </c>
       <c r="R12" t="n">
-        <v>7378006</v>
+        <v>7377974</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1800,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464168</v>
+        <v>124464171</v>
       </c>
       <c r="B13" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878777</v>
+        <v>878938</v>
       </c>
       <c r="R13" t="n">
-        <v>7377974</v>
+        <v>7377766</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1914,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464333</v>
+        <v>124464172</v>
       </c>
       <c r="B14" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879031</v>
+        <v>879038</v>
       </c>
       <c r="R14" t="n">
-        <v>7377846</v>
+        <v>7377791</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2004,22 +2009,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464172</v>
+        <v>124464331</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2032,16 +2037,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879038</v>
+        <v>878850</v>
       </c>
       <c r="R15" t="n">
-        <v>7377791</v>
+        <v>7378069</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2094,6 +2099,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2106,22 +2116,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464170</v>
+        <v>124464339</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2140,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878795</v>
+        <v>878916</v>
       </c>
       <c r="R16" t="n">
-        <v>7377998</v>
+        <v>7377843</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2208,22 +2218,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464340</v>
+        <v>124464165</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2242,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878814</v>
+        <v>878976</v>
       </c>
       <c r="R17" t="n">
-        <v>7378040</v>
+        <v>7377902</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2298,6 +2308,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2310,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464331</v>
+        <v>124464174</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>92490</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878850</v>
+        <v>878886</v>
       </c>
       <c r="R18" t="n">
-        <v>7378069</v>
+        <v>7377893</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2400,11 +2415,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2417,19 +2427,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464166</v>
+        <v>124464170</v>
       </c>
       <c r="B19" t="n">
         <v>79920</v>
@@ -2469,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878884</v>
+        <v>878795</v>
       </c>
       <c r="R19" t="n">
-        <v>7377762</v>
+        <v>7377998</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2531,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464165</v>
+        <v>124464178</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2543,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878976</v>
+        <v>878957</v>
       </c>
       <c r="R20" t="n">
-        <v>7377902</v>
+        <v>7377759</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2607,11 +2617,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464332</v>
+        <v>124464338</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878883</v>
+        <v>878878</v>
       </c>
       <c r="R21" t="n">
-        <v>7377894</v>
+        <v>7378047</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2716,11 +2721,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2742,6 +2742,113 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125110092</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56714</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pölkkyjänkkä, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>879067</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7377975</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk, Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464336</v>
+        <v>124464176</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878805</v>
+        <v>878858</v>
       </c>
       <c r="R4" t="n">
-        <v>7377987</v>
+        <v>7377931</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -962,11 +962,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464176</v>
+        <v>124464336</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878858</v>
+        <v>878805</v>
       </c>
       <c r="R5" t="n">
-        <v>7377931</v>
+        <v>7377987</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1069,6 +1064,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1081,12 +1081,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464172</v>
+        <v>124464331</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,16 +1935,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879038</v>
+        <v>878850</v>
       </c>
       <c r="R14" t="n">
-        <v>7377791</v>
+        <v>7378069</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1997,6 +1997,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2009,22 +2014,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464331</v>
+        <v>124464172</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,16 +2042,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878850</v>
+        <v>879038</v>
       </c>
       <c r="R15" t="n">
-        <v>7378069</v>
+        <v>7377791</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2099,11 +2104,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2116,12 +2116,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464333</v>
+        <v>124464171</v>
       </c>
       <c r="B2" t="n">
         <v>91023</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879031</v>
+        <v>878938</v>
       </c>
       <c r="R2" t="n">
-        <v>7377846</v>
+        <v>7377766</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464332</v>
+        <v>124464177</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878883</v>
+        <v>879054</v>
       </c>
       <c r="R3" t="n">
-        <v>7377894</v>
+        <v>7377801</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464176</v>
+        <v>124464165</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878858</v>
+        <v>878976</v>
       </c>
       <c r="R4" t="n">
-        <v>7377931</v>
+        <v>7377902</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464336</v>
+        <v>124464174</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>92490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878805</v>
+        <v>878886</v>
       </c>
       <c r="R5" t="n">
-        <v>7377987</v>
+        <v>7377893</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1064,11 +1069,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1081,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464177</v>
+        <v>124464168</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879054</v>
+        <v>878777</v>
       </c>
       <c r="R6" t="n">
-        <v>7377801</v>
+        <v>7377974</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464340</v>
+        <v>124464166</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878814</v>
+        <v>878884</v>
       </c>
       <c r="R7" t="n">
-        <v>7378040</v>
+        <v>7377762</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1290,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464335</v>
+        <v>124464339</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>879043</v>
+        <v>878916</v>
       </c>
       <c r="R8" t="n">
-        <v>7377785</v>
+        <v>7377843</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1378,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464180</v>
+        <v>124464333</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878981</v>
+        <v>879031</v>
       </c>
       <c r="R9" t="n">
-        <v>7377864</v>
+        <v>7377846</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1499,12 +1489,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1613,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464166</v>
+        <v>124464335</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878884</v>
+        <v>879043</v>
       </c>
       <c r="R11" t="n">
-        <v>7377762</v>
+        <v>7377785</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1691,6 +1681,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1703,22 +1698,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464168</v>
+        <v>124464340</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878777</v>
+        <v>878814</v>
       </c>
       <c r="R12" t="n">
-        <v>7377974</v>
+        <v>7378040</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1805,22 +1800,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464171</v>
+        <v>124464180</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1824,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878938</v>
+        <v>878981</v>
       </c>
       <c r="R13" t="n">
-        <v>7377766</v>
+        <v>7377864</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1919,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464331</v>
+        <v>124464172</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,16 +1930,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1959,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878850</v>
+        <v>879038</v>
       </c>
       <c r="R14" t="n">
-        <v>7378069</v>
+        <v>7377791</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1997,11 +1992,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2014,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464172</v>
+        <v>124464332</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879038</v>
+        <v>878883</v>
       </c>
       <c r="R15" t="n">
-        <v>7377791</v>
+        <v>7377894</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2104,6 +2094,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2116,22 +2111,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464339</v>
+        <v>124464338</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878916</v>
+        <v>878878</v>
       </c>
       <c r="R16" t="n">
-        <v>7377843</v>
+        <v>7378047</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2230,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464165</v>
+        <v>124464336</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878976</v>
+        <v>878805</v>
       </c>
       <c r="R17" t="n">
-        <v>7377902</v>
+        <v>7377987</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,7 +2305,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>0.5 m2</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464174</v>
+        <v>124464170</v>
       </c>
       <c r="B18" t="n">
-        <v>92490</v>
+        <v>79920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878886</v>
+        <v>878795</v>
       </c>
       <c r="R18" t="n">
-        <v>7377893</v>
+        <v>7377998</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2439,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464170</v>
+        <v>124464331</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878795</v>
+        <v>878850</v>
       </c>
       <c r="R19" t="n">
-        <v>7377998</v>
+        <v>7378069</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2517,6 +2512,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2529,22 +2529,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464178</v>
+        <v>124464176</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878957</v>
+        <v>878858</v>
       </c>
       <c r="R20" t="n">
-        <v>7377759</v>
+        <v>7377931</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464338</v>
+        <v>124464178</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878878</v>
+        <v>878957</v>
       </c>
       <c r="R21" t="n">
-        <v>7378047</v>
+        <v>7377759</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464171</v>
+        <v>124464176</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878938</v>
+        <v>878858</v>
       </c>
       <c r="R2" t="n">
-        <v>7377766</v>
+        <v>7377931</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464177</v>
+        <v>124464332</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879054</v>
+        <v>878883</v>
       </c>
       <c r="R3" t="n">
-        <v>7377801</v>
+        <v>7377894</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464165</v>
+        <v>124464335</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878976</v>
+        <v>879043</v>
       </c>
       <c r="R4" t="n">
-        <v>7377902</v>
+        <v>7377785</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464174</v>
+        <v>124464165</v>
       </c>
       <c r="B5" t="n">
-        <v>92490</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878886</v>
+        <v>878976</v>
       </c>
       <c r="R5" t="n">
-        <v>7377893</v>
+        <v>7377902</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1067,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464168</v>
+        <v>124464333</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878777</v>
+        <v>879031</v>
       </c>
       <c r="R6" t="n">
-        <v>7377974</v>
+        <v>7377846</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1183,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464166</v>
+        <v>124464331</v>
       </c>
       <c r="B7" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878884</v>
+        <v>878850</v>
       </c>
       <c r="R7" t="n">
-        <v>7377762</v>
+        <v>7378069</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1273,6 +1278,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1285,19 +1295,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464339</v>
+        <v>124464340</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1337,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878916</v>
+        <v>878814</v>
       </c>
       <c r="R8" t="n">
-        <v>7377843</v>
+        <v>7378040</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464333</v>
+        <v>124464171</v>
       </c>
       <c r="B9" t="n">
         <v>91023</v>
@@ -1439,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879031</v>
+        <v>878938</v>
       </c>
       <c r="R9" t="n">
-        <v>7377846</v>
+        <v>7377766</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1489,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464334</v>
+        <v>124464178</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878794</v>
+        <v>878957</v>
       </c>
       <c r="R10" t="n">
-        <v>7378006</v>
+        <v>7377759</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1591,22 +1601,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464335</v>
+        <v>124464334</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879043</v>
+        <v>878794</v>
       </c>
       <c r="R11" t="n">
-        <v>7377785</v>
+        <v>7378006</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1679,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464340</v>
+        <v>124464166</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878814</v>
+        <v>878884</v>
       </c>
       <c r="R12" t="n">
-        <v>7378040</v>
+        <v>7377762</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1800,22 +1805,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464180</v>
+        <v>124464336</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1824,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878981</v>
+        <v>878805</v>
       </c>
       <c r="R13" t="n">
-        <v>7377864</v>
+        <v>7377987</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1890,6 +1895,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1902,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464172</v>
+        <v>124464338</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,16 +1940,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1954,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>879038</v>
+        <v>878878</v>
       </c>
       <c r="R14" t="n">
-        <v>7377791</v>
+        <v>7378047</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2004,22 +2014,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464332</v>
+        <v>124464174</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>92490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2028,25 +2038,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2056,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878883</v>
+        <v>878886</v>
       </c>
       <c r="R15" t="n">
-        <v>7377894</v>
+        <v>7377893</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2094,11 +2104,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2111,22 +2116,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464338</v>
+        <v>124464172</v>
       </c>
       <c r="B16" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,16 +2144,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878878</v>
+        <v>879038</v>
       </c>
       <c r="R16" t="n">
-        <v>7378047</v>
+        <v>7377791</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2213,19 +2218,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464336</v>
+        <v>124464177</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878805</v>
+        <v>879054</v>
       </c>
       <c r="R17" t="n">
-        <v>7377987</v>
+        <v>7377801</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2305,7 +2310,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.5 m2</t>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2320,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464170</v>
+        <v>124464339</v>
       </c>
       <c r="B18" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2349,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878795</v>
+        <v>878916</v>
       </c>
       <c r="R18" t="n">
-        <v>7377998</v>
+        <v>7377843</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2422,22 +2427,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464331</v>
+        <v>124464168</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2451,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878850</v>
+        <v>878777</v>
       </c>
       <c r="R19" t="n">
-        <v>7378069</v>
+        <v>7377974</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2512,11 +2517,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2529,22 +2529,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464176</v>
+        <v>124464170</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>79920</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878858</v>
+        <v>878795</v>
       </c>
       <c r="R20" t="n">
-        <v>7377931</v>
+        <v>7377998</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464178</v>
+        <v>124464180</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878957</v>
+        <v>878981</v>
       </c>
       <c r="R21" t="n">
-        <v>7377759</v>
+        <v>7377864</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464332</v>
+        <v>124464335</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878883</v>
+        <v>879043</v>
       </c>
       <c r="R3" t="n">
-        <v>7377894</v>
+        <v>7377785</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464335</v>
+        <v>124464332</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879043</v>
+        <v>878883</v>
       </c>
       <c r="R4" t="n">
-        <v>7377785</v>
+        <v>7377894</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464174</v>
+        <v>124464172</v>
       </c>
       <c r="B15" t="n">
-        <v>92490</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878886</v>
+        <v>879038</v>
       </c>
       <c r="R15" t="n">
-        <v>7377893</v>
+        <v>7377791</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464172</v>
+        <v>124464174</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>92490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879038</v>
+        <v>878886</v>
       </c>
       <c r="R16" t="n">
-        <v>7377791</v>
+        <v>7377893</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464172</v>
+        <v>124464174</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>92490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>879038</v>
+        <v>878886</v>
       </c>
       <c r="R15" t="n">
-        <v>7377791</v>
+        <v>7377893</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464174</v>
+        <v>124464172</v>
       </c>
       <c r="B16" t="n">
-        <v>92490</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878886</v>
+        <v>879038</v>
       </c>
       <c r="R16" t="n">
-        <v>7377893</v>
+        <v>7377791</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464176</v>
+        <v>124464336</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878858</v>
+        <v>878805</v>
       </c>
       <c r="R2" t="n">
-        <v>7377931</v>
+        <v>7377987</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,6 +753,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464335</v>
+        <v>124464178</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>879043</v>
+        <v>878957</v>
       </c>
       <c r="R3" t="n">
-        <v>7377785</v>
+        <v>7377759</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,11 +860,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464332</v>
+        <v>124464180</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878883</v>
+        <v>878981</v>
       </c>
       <c r="R4" t="n">
-        <v>7377894</v>
+        <v>7377864</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -962,11 +962,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464165</v>
+        <v>124464338</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878976</v>
+        <v>878878</v>
       </c>
       <c r="R5" t="n">
-        <v>7377902</v>
+        <v>7378047</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1069,11 +1064,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1086,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464333</v>
+        <v>124464172</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879031</v>
+        <v>879038</v>
       </c>
       <c r="R6" t="n">
-        <v>7377846</v>
+        <v>7377791</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1188,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464331</v>
+        <v>124464177</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878850</v>
+        <v>879054</v>
       </c>
       <c r="R7" t="n">
-        <v>7378069</v>
+        <v>7377801</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1270,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464340</v>
+        <v>124464171</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878814</v>
+        <v>878938</v>
       </c>
       <c r="R8" t="n">
-        <v>7378040</v>
+        <v>7377766</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1397,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464171</v>
+        <v>124464339</v>
       </c>
       <c r="B9" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1411,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878938</v>
+        <v>878916</v>
       </c>
       <c r="R9" t="n">
-        <v>7377766</v>
+        <v>7377843</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1499,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464178</v>
+        <v>124464170</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878957</v>
+        <v>878795</v>
       </c>
       <c r="R10" t="n">
-        <v>7377759</v>
+        <v>7377998</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1715,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464166</v>
+        <v>124464333</v>
       </c>
       <c r="B12" t="n">
-        <v>79920</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878884</v>
+        <v>879031</v>
       </c>
       <c r="R12" t="n">
-        <v>7377762</v>
+        <v>7377846</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1805,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464336</v>
+        <v>124464176</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878805</v>
+        <v>878858</v>
       </c>
       <c r="R13" t="n">
-        <v>7377987</v>
+        <v>7377931</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1895,11 +1885,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1912,22 +1897,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464338</v>
+        <v>124464168</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1921,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878878</v>
+        <v>878777</v>
       </c>
       <c r="R14" t="n">
-        <v>7378047</v>
+        <v>7377974</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2014,22 +1999,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464174</v>
+        <v>124464331</v>
       </c>
       <c r="B15" t="n">
-        <v>92490</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2027,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878886</v>
+        <v>878850</v>
       </c>
       <c r="R15" t="n">
-        <v>7377893</v>
+        <v>7378069</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2104,6 +2089,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2116,22 +2106,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464172</v>
+        <v>124464166</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>879038</v>
+        <v>878884</v>
       </c>
       <c r="R16" t="n">
-        <v>7377791</v>
+        <v>7377762</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2230,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464177</v>
+        <v>124464332</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2242,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>879054</v>
+        <v>878883</v>
       </c>
       <c r="R17" t="n">
-        <v>7377801</v>
+        <v>7377894</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2310,7 +2300,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2325,22 +2315,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464339</v>
+        <v>124464174</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878916</v>
+        <v>878886</v>
       </c>
       <c r="R18" t="n">
-        <v>7377843</v>
+        <v>7377893</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2427,22 +2417,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464168</v>
+        <v>124464340</v>
       </c>
       <c r="B19" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878777</v>
+        <v>878814</v>
       </c>
       <c r="R19" t="n">
-        <v>7377974</v>
+        <v>7378040</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2529,22 +2519,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464170</v>
+        <v>124464165</v>
       </c>
       <c r="B20" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878795</v>
+        <v>878976</v>
       </c>
       <c r="R20" t="n">
-        <v>7377998</v>
+        <v>7377902</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2617,6 +2607,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464180</v>
+        <v>124464335</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878981</v>
+        <v>879043</v>
       </c>
       <c r="R21" t="n">
-        <v>7377864</v>
+        <v>7377785</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2721,6 +2716,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464336</v>
+        <v>124464165</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878805</v>
+        <v>878976</v>
       </c>
       <c r="R2" t="n">
-        <v>7377987</v>
+        <v>7377902</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5 m2</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464178</v>
+        <v>124464176</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878957</v>
+        <v>878858</v>
       </c>
       <c r="R3" t="n">
-        <v>7377759</v>
+        <v>7377931</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464180</v>
+        <v>124464168</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878981</v>
+        <v>878777</v>
       </c>
       <c r="R4" t="n">
-        <v>7377864</v>
+        <v>7377974</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464338</v>
+        <v>124464166</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>79920</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878878</v>
+        <v>878884</v>
       </c>
       <c r="R5" t="n">
-        <v>7378047</v>
+        <v>7377762</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464177</v>
+        <v>124464339</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879054</v>
+        <v>878916</v>
       </c>
       <c r="R7" t="n">
-        <v>7377801</v>
+        <v>7377843</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1268,11 +1268,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1285,22 +1280,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464171</v>
+        <v>124464178</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1304,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878938</v>
+        <v>878957</v>
       </c>
       <c r="R8" t="n">
-        <v>7377766</v>
+        <v>7377759</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464339</v>
+        <v>124464177</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878916</v>
+        <v>879054</v>
       </c>
       <c r="R9" t="n">
-        <v>7377843</v>
+        <v>7377801</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1477,6 +1472,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1489,22 +1489,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464170</v>
+        <v>124464174</v>
       </c>
       <c r="B10" t="n">
-        <v>79920</v>
+        <v>92490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878795</v>
+        <v>878886</v>
       </c>
       <c r="R10" t="n">
-        <v>7377998</v>
+        <v>7377893</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464334</v>
+        <v>124464340</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878794</v>
+        <v>878814</v>
       </c>
       <c r="R11" t="n">
-        <v>7378006</v>
+        <v>7378040</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1705,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464333</v>
+        <v>124464180</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879031</v>
+        <v>878981</v>
       </c>
       <c r="R12" t="n">
-        <v>7377846</v>
+        <v>7377864</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1795,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464176</v>
+        <v>124464335</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878858</v>
+        <v>879043</v>
       </c>
       <c r="R13" t="n">
-        <v>7377931</v>
+        <v>7377785</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1885,6 +1885,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1897,22 +1902,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464168</v>
+        <v>124464338</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1921,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878777</v>
+        <v>878878</v>
       </c>
       <c r="R14" t="n">
-        <v>7377974</v>
+        <v>7378047</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464331</v>
+        <v>124464171</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2028,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878850</v>
+        <v>878938</v>
       </c>
       <c r="R15" t="n">
-        <v>7378069</v>
+        <v>7377766</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2089,11 +2094,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2106,22 +2106,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464166</v>
+        <v>124464331</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878884</v>
+        <v>878850</v>
       </c>
       <c r="R16" t="n">
-        <v>7377762</v>
+        <v>7378069</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2196,6 +2196,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2208,22 +2213,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464332</v>
+        <v>124464336</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878883</v>
+        <v>878805</v>
       </c>
       <c r="R17" t="n">
-        <v>7377894</v>
+        <v>7377987</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2300,7 +2305,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>0.5 m2</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464174</v>
+        <v>124464334</v>
       </c>
       <c r="B18" t="n">
-        <v>92490</v>
+        <v>91023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878886</v>
+        <v>878794</v>
       </c>
       <c r="R18" t="n">
-        <v>7377893</v>
+        <v>7378006</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2417,22 +2422,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464340</v>
+        <v>124464333</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878814</v>
+        <v>879031</v>
       </c>
       <c r="R19" t="n">
-        <v>7378040</v>
+        <v>7377846</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2531,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464165</v>
+        <v>124464332</v>
       </c>
       <c r="B20" t="n">
         <v>56722</v>
@@ -2571,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878976</v>
+        <v>878883</v>
       </c>
       <c r="R20" t="n">
-        <v>7377902</v>
+        <v>7377894</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2626,22 +2631,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464335</v>
+        <v>124464170</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2650,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>879043</v>
+        <v>878795</v>
       </c>
       <c r="R21" t="n">
-        <v>7377785</v>
+        <v>7377998</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2716,11 +2721,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464165</v>
+        <v>124464335</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878976</v>
+        <v>879043</v>
       </c>
       <c r="R2" t="n">
-        <v>7377902</v>
+        <v>7377785</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464176</v>
+        <v>124464331</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878858</v>
+        <v>878850</v>
       </c>
       <c r="R3" t="n">
-        <v>7377931</v>
+        <v>7378069</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,6 +860,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464168</v>
+        <v>124464176</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878777</v>
+        <v>878858</v>
       </c>
       <c r="R4" t="n">
-        <v>7377974</v>
+        <v>7377931</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464166</v>
+        <v>124464340</v>
       </c>
       <c r="B5" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878884</v>
+        <v>878814</v>
       </c>
       <c r="R5" t="n">
-        <v>7377762</v>
+        <v>7378040</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1076,22 +1081,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464172</v>
+        <v>124464336</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>879038</v>
+        <v>878805</v>
       </c>
       <c r="R6" t="n">
-        <v>7377791</v>
+        <v>7377987</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1166,6 +1171,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1178,22 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464339</v>
+        <v>124464177</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878916</v>
+        <v>879054</v>
       </c>
       <c r="R7" t="n">
-        <v>7377843</v>
+        <v>7377801</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1268,6 +1278,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1280,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464178</v>
+        <v>124464168</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878957</v>
+        <v>878777</v>
       </c>
       <c r="R8" t="n">
-        <v>7377759</v>
+        <v>7377974</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1394,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464177</v>
+        <v>124464339</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>879054</v>
+        <v>878916</v>
       </c>
       <c r="R9" t="n">
-        <v>7377801</v>
+        <v>7377843</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1472,11 +1487,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1489,22 +1499,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464174</v>
+        <v>124464180</v>
       </c>
       <c r="B10" t="n">
-        <v>92490</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878886</v>
+        <v>878981</v>
       </c>
       <c r="R10" t="n">
-        <v>7377893</v>
+        <v>7377864</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464340</v>
+        <v>124464170</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878814</v>
+        <v>878795</v>
       </c>
       <c r="R11" t="n">
-        <v>7378040</v>
+        <v>7377998</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1693,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464180</v>
+        <v>124464165</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878981</v>
+        <v>878976</v>
       </c>
       <c r="R12" t="n">
-        <v>7377864</v>
+        <v>7377902</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1781,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464335</v>
+        <v>124464332</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879043</v>
+        <v>878883</v>
       </c>
       <c r="R13" t="n">
-        <v>7377785</v>
+        <v>7377894</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1887,7 +1902,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Bohål</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464338</v>
+        <v>124464178</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1941,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878878</v>
+        <v>878957</v>
       </c>
       <c r="R14" t="n">
-        <v>7378047</v>
+        <v>7377759</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2004,12 +2019,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2118,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464331</v>
+        <v>124464166</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2145,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878850</v>
+        <v>878884</v>
       </c>
       <c r="R16" t="n">
-        <v>7378069</v>
+        <v>7377762</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2196,11 +2211,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2213,22 +2223,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464336</v>
+        <v>124464172</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,25 +2247,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878805</v>
+        <v>879038</v>
       </c>
       <c r="R17" t="n">
-        <v>7377987</v>
+        <v>7377791</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2303,11 +2313,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2320,19 +2325,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464334</v>
+        <v>124464333</v>
       </c>
       <c r="B18" t="n">
         <v>91023</v>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878794</v>
+        <v>879031</v>
       </c>
       <c r="R18" t="n">
-        <v>7378006</v>
+        <v>7377846</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2434,7 +2439,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464333</v>
+        <v>124464334</v>
       </c>
       <c r="B19" t="n">
         <v>91023</v>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>879031</v>
+        <v>878794</v>
       </c>
       <c r="R19" t="n">
-        <v>7377846</v>
+        <v>7378006</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2536,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464332</v>
+        <v>124464338</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878883</v>
+        <v>878878</v>
       </c>
       <c r="R20" t="n">
-        <v>7377894</v>
+        <v>7378047</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2612,11 +2617,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464170</v>
+        <v>124464174</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>92490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878795</v>
+        <v>878886</v>
       </c>
       <c r="R21" t="n">
-        <v>7377998</v>
+        <v>7377893</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464335</v>
+        <v>124464339</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>879043</v>
+        <v>878916</v>
       </c>
       <c r="R2" t="n">
-        <v>7377785</v>
+        <v>7377843</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464331</v>
+        <v>124464165</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878850</v>
+        <v>878976</v>
       </c>
       <c r="R3" t="n">
-        <v>7378069</v>
+        <v>7377902</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Avbarkad gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464176</v>
+        <v>124464177</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>878858</v>
+        <v>879054</v>
       </c>
       <c r="R4" t="n">
-        <v>7377931</v>
+        <v>7377801</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464340</v>
+        <v>124464334</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878814</v>
+        <v>878794</v>
       </c>
       <c r="R5" t="n">
-        <v>7378040</v>
+        <v>7378006</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464336</v>
+        <v>124464180</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878805</v>
+        <v>878981</v>
       </c>
       <c r="R6" t="n">
-        <v>7377987</v>
+        <v>7377864</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1171,11 +1171,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0.5 m2</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1188,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464177</v>
+        <v>124464176</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>879054</v>
+        <v>878858</v>
       </c>
       <c r="R7" t="n">
-        <v>7377801</v>
+        <v>7377931</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1276,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464168</v>
+        <v>124464340</v>
       </c>
       <c r="B8" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878777</v>
+        <v>878814</v>
       </c>
       <c r="R8" t="n">
-        <v>7377974</v>
+        <v>7378040</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1397,22 +1387,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464339</v>
+        <v>124464338</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878916</v>
+        <v>878878</v>
       </c>
       <c r="R9" t="n">
-        <v>7377843</v>
+        <v>7378047</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464180</v>
+        <v>124464171</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878981</v>
+        <v>878938</v>
       </c>
       <c r="R10" t="n">
-        <v>7377864</v>
+        <v>7377766</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1613,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464170</v>
+        <v>124464172</v>
       </c>
       <c r="B11" t="n">
-        <v>79920</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1615,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>878795</v>
+        <v>879038</v>
       </c>
       <c r="R11" t="n">
-        <v>7377998</v>
+        <v>7377791</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1715,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464165</v>
+        <v>124464333</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>878976</v>
+        <v>879031</v>
       </c>
       <c r="R12" t="n">
-        <v>7377902</v>
+        <v>7377846</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1793,11 +1783,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1810,22 +1795,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464332</v>
+        <v>124464335</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>878883</v>
+        <v>879043</v>
       </c>
       <c r="R13" t="n">
-        <v>7377894</v>
+        <v>7377785</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1902,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464178</v>
+        <v>124464166</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,25 +1926,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878957</v>
+        <v>878884</v>
       </c>
       <c r="R14" t="n">
-        <v>7377759</v>
+        <v>7377762</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2031,10 +2016,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464171</v>
+        <v>124464170</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>79920</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878938</v>
+        <v>878795</v>
       </c>
       <c r="R15" t="n">
-        <v>7377766</v>
+        <v>7377998</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2133,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464166</v>
+        <v>124464174</v>
       </c>
       <c r="B16" t="n">
-        <v>79920</v>
+        <v>92490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2130,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878884</v>
+        <v>878886</v>
       </c>
       <c r="R16" t="n">
-        <v>7377762</v>
+        <v>7377893</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2235,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464172</v>
+        <v>124464332</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,25 +2232,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>879038</v>
+        <v>878883</v>
       </c>
       <c r="R17" t="n">
-        <v>7377791</v>
+        <v>7377894</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2313,6 +2298,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2325,22 +2315,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464333</v>
+        <v>124464331</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>879031</v>
+        <v>878850</v>
       </c>
       <c r="R18" t="n">
-        <v>7377846</v>
+        <v>7378069</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2413,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464334</v>
+        <v>124464178</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878794</v>
+        <v>878957</v>
       </c>
       <c r="R19" t="n">
-        <v>7378006</v>
+        <v>7377759</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2529,22 +2524,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464338</v>
+        <v>124464336</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,25 +2548,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878878</v>
+        <v>878805</v>
       </c>
       <c r="R20" t="n">
-        <v>7378047</v>
+        <v>7377987</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2617,6 +2612,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464174</v>
+        <v>124464168</v>
       </c>
       <c r="B21" t="n">
-        <v>92490</v>
+        <v>79920</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878886</v>
+        <v>878777</v>
       </c>
       <c r="R21" t="n">
-        <v>7377893</v>
+        <v>7377974</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124464339</v>
+        <v>124464336</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>878916</v>
+        <v>878805</v>
       </c>
       <c r="R2" t="n">
-        <v>7377843</v>
+        <v>7377987</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5 m2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124464165</v>
+        <v>124464338</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>878976</v>
+        <v>878878</v>
       </c>
       <c r="R3" t="n">
-        <v>7377902</v>
+        <v>7378047</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,11 +860,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124464177</v>
+        <v>124464333</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>879054</v>
+        <v>879031</v>
       </c>
       <c r="R4" t="n">
-        <v>7377801</v>
+        <v>7377846</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -962,11 +962,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 kvm</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -979,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124464334</v>
+        <v>124464331</v>
       </c>
       <c r="B5" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>878794</v>
+        <v>878850</v>
       </c>
       <c r="R5" t="n">
-        <v>7378006</v>
+        <v>7378069</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Avbarkad gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124464180</v>
+        <v>124464174</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>92490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>878981</v>
+        <v>878886</v>
       </c>
       <c r="R6" t="n">
-        <v>7377864</v>
+        <v>7377893</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124464176</v>
+        <v>124464334</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>878858</v>
+        <v>878794</v>
       </c>
       <c r="R7" t="n">
-        <v>7377931</v>
+        <v>7378006</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1285,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124464340</v>
+        <v>124464332</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>878814</v>
+        <v>878883</v>
       </c>
       <c r="R8" t="n">
-        <v>7378040</v>
+        <v>7377894</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1373,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464338</v>
+        <v>124464339</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>878878</v>
+        <v>878916</v>
       </c>
       <c r="R9" t="n">
-        <v>7378047</v>
+        <v>7377843</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464171</v>
+        <v>124464176</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1205</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>878938</v>
+        <v>878858</v>
       </c>
       <c r="R10" t="n">
-        <v>7377766</v>
+        <v>7377931</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1603,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464172</v>
+        <v>124464335</v>
       </c>
       <c r="B11" t="n">
         <v>57529</v>
@@ -1643,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>879038</v>
+        <v>879043</v>
       </c>
       <c r="R11" t="n">
-        <v>7377791</v>
+        <v>7377785</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1681,6 +1686,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1693,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464333</v>
+        <v>124464177</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1205</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>879031</v>
+        <v>879054</v>
       </c>
       <c r="R12" t="n">
-        <v>7377846</v>
+        <v>7377801</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1783,6 +1793,11 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 kvm</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1795,22 +1810,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464335</v>
+        <v>124464170</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>79920</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1819,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>879043</v>
+        <v>878795</v>
       </c>
       <c r="R13" t="n">
-        <v>7377785</v>
+        <v>7377998</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1885,11 +1900,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Bohål</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1902,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464166</v>
+        <v>124464178</v>
       </c>
       <c r="B14" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1926,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>878884</v>
+        <v>878957</v>
       </c>
       <c r="R14" t="n">
-        <v>7377762</v>
+        <v>7377759</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2016,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464170</v>
+        <v>124464166</v>
       </c>
       <c r="B15" t="n">
         <v>79920</v>
@@ -2056,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>878795</v>
+        <v>878884</v>
       </c>
       <c r="R15" t="n">
-        <v>7377998</v>
+        <v>7377762</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464174</v>
+        <v>124464168</v>
       </c>
       <c r="B16" t="n">
-        <v>92490</v>
+        <v>79920</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,25 +2140,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>878886</v>
+        <v>878777</v>
       </c>
       <c r="R16" t="n">
-        <v>7377893</v>
+        <v>7377974</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2220,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464332</v>
+        <v>124464171</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
+        <v>91023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>878883</v>
+        <v>878938</v>
       </c>
       <c r="R17" t="n">
-        <v>7377894</v>
+        <v>7377766</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2298,11 +2308,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2315,22 +2320,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464331</v>
+        <v>124464180</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>878850</v>
+        <v>878981</v>
       </c>
       <c r="R18" t="n">
-        <v>7378069</v>
+        <v>7377864</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2405,11 +2410,6 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Avbarkad gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2422,22 +2422,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464178</v>
+        <v>124464172</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>878957</v>
+        <v>879038</v>
       </c>
       <c r="R19" t="n">
-        <v>7377759</v>
+        <v>7377791</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464336</v>
+        <v>124464165</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2548,25 +2548,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>878805</v>
+        <v>878976</v>
       </c>
       <c r="R20" t="n">
-        <v>7377987</v>
+        <v>7377902</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.5 m2</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2631,22 +2631,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nicholas Nygren</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124464168</v>
+        <v>124464340</v>
       </c>
       <c r="B21" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2655,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>878777</v>
+        <v>878814</v>
       </c>
       <c r="R21" t="n">
-        <v>7377974</v>
+        <v>7378040</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2733,12 +2733,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Nicholas Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -2748,7 +2748,7 @@
         <v>125110092</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>56828</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -2748,12 +2748,7 @@
         <v>125110092</v>
       </c>
       <c r="B22" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>124464332</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>124464165</v>
       </c>
       <c r="B20" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>124464332</v>
       </c>
       <c r="B8" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>124464165</v>
       </c>
       <c r="B20" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>124464332</v>
       </c>
       <c r="B8" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>124464165</v>
       </c>
       <c r="B20" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 18577-2021 artfynd.xlsx
+++ b/artfynd/A 18577-2021 artfynd.xlsx
@@ -1300,7 +1300,7 @@
         <v>124464332</v>
       </c>
       <c r="B8" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>124464165</v>
       </c>
       <c r="B20" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
